--- a/Harga Custom TLJ.xlsx
+++ b/Harga Custom TLJ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD3255A-4AE2-4856-917C-46C08ED3BDC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DBC729D-882B-47C6-9AE2-8A701EDA93CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0865E421-8F7D-413A-8289-E92414008AEA}"/>
+    <workbookView xWindow="3375" yWindow="2835" windowWidth="15360" windowHeight="8085" xr2:uid="{0865E421-8F7D-413A-8289-E92414008AEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="90">
   <si>
     <t>Nama Produk</t>
   </si>
@@ -286,6 +286,15 @@
   </si>
   <si>
     <t>Alquran Edisi Tahlilan Lebih Mulia Daripada Buku Yasin Biasa | Al Aqeel A6 Kertas HVS | SURABAYA |</t>
+  </si>
+  <si>
+    <t>Custom Al Quran Terjemah Faheem A5 Kertas Koran | Alquran Wakaf Hadiah Hampers | Semarang</t>
+  </si>
+  <si>
+    <t>1 sisipan</t>
+  </si>
+  <si>
+    <t>2 sisipan</t>
   </si>
 </sst>
 </file>
@@ -698,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3868EE60-3048-4482-B09F-8FE75025847A}">
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultColWidth="16.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="98.140625" bestFit="1" customWidth="1"/>
@@ -1627,6 +1636,28 @@
         <v>2000</v>
       </c>
     </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84" t="s">
+        <v>88</v>
+      </c>
+      <c r="C84">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>87</v>
+      </c>
+      <c r="B85" t="s">
+        <v>89</v>
+      </c>
+      <c r="C85">
+        <v>3000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
